--- a/figures/rq2/agent-harness-distribution.xlsx
+++ b/figures/rq2/agent-harness-distribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\STG\what-are-they-doing\figures\rq2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FDA530E-1302-43FB-A85A-8816EE93638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9A6DA58F-DB5B-4C37-B6F3-DF26C20A0836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24789" yWindow="5743" windowWidth="24892" windowHeight="15634" xr2:uid="{A9BDEA09-76A8-4D12-A73E-92A55D0F5EBD}"/>
   </bookViews>
@@ -662,7 +662,296 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1137,11 +1426,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'agent-harness-distribution'!$1:$1</c15:sqref>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1:$XFD$1)</c:f>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
               <c:strCache>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
@@ -1195,21 +1484,21 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('agent-harness-distribution'!$E$3,'agent-harness-distribution'!$G$3,'agent-harness-distribution'!$I$3,'agent-harness-distribution'!$K$3,'agent-harness-distribution'!$M$3,'agent-harness-distribution'!$O$3,'agent-harness-distribution'!$Q$3,'agent-harness-distribution'!$S$3,'agent-harness-distribution'!$U$3,'agent-harness-distribution'!$W$3,'agent-harness-distribution'!$Y$3,'agent-harness-distribution'!$AA$3)</c:f>
+              <c:f>('agent-harness-distribution'!$D$3,'agent-harness-distribution'!$F$3,'agent-harness-distribution'!$H$3,'agent-harness-distribution'!$J$3,'agent-harness-distribution'!$L$3,'agent-harness-distribution'!$N$3,'agent-harness-distribution'!$P$3,'agent-harness-distribution'!$R$3,'agent-harness-distribution'!$T$3,'agent-harness-distribution'!$V$3,'agent-harness-distribution'!$X$3,'agent-harness-distribution'!$Z$3,'agent-harness-distribution'!$AB$3)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2039</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>23.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>349</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1218,13 +1507,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>142</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6086</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>70.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -1233,6 +1522,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1241,6 +1533,2660 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-736D-4701-843B-463F9682FE98}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>mavam</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$3:$AB$3</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$3,'agent-harness-distribution'!$F$3,'agent-harness-distribution'!$H$3,'agent-harness-distribution'!$J$3,'agent-harness-distribution'!$L$3,'agent-harness-distribution'!$N$3,'agent-harness-distribution'!$P$3,'agent-harness-distribution'!$R$3,'agent-harness-distribution'!$T$3,'agent-harness-distribution'!$V$3,'agent-harness-distribution'!$X$3,'agent-harness-distribution'!$Z$3,'agent-harness-distribution'!$AB$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1F73-400C-B742-4E4E543EB409}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>obra</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$5:$AB$5</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$5,'agent-harness-distribution'!$F$5,'agent-harness-distribution'!$H$5,'agent-harness-distribution'!$J$5,'agent-harness-distribution'!$L$5,'agent-harness-distribution'!$N$5,'agent-harness-distribution'!$P$5,'agent-harness-distribution'!$R$5,'agent-harness-distribution'!$T$5,'agent-harness-distribution'!$V$5,'agent-harness-distribution'!$X$5,'agent-harness-distribution'!$Z$5,'agent-harness-distribution'!$AB$5)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C123-4BCF-ABF3-2A65E96F14FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>philipp-spiess</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$6:$AB$6</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$6,'agent-harness-distribution'!$F$6,'agent-harness-distribution'!$H$6,'agent-harness-distribution'!$J$6,'agent-harness-distribution'!$L$6,'agent-harness-distribution'!$N$6,'agent-harness-distribution'!$P$6,'agent-harness-distribution'!$R$6,'agent-harness-distribution'!$T$6,'agent-harness-distribution'!$V$6,'agent-harness-distribution'!$X$6,'agent-harness-distribution'!$Z$6,'agent-harness-distribution'!$AB$6)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>95.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8E55-4C90-B8FC-1156D09D8EAF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>ruvnet</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ruvnet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$7:$AB$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$7,'agent-harness-distribution'!$F$7,'agent-harness-distribution'!$H$7,'agent-harness-distribution'!$J$7,'agent-harness-distribution'!$L$7,'agent-harness-distribution'!$N$7,'agent-harness-distribution'!$P$7,'agent-harness-distribution'!$R$7,'agent-harness-distribution'!$T$7,'agent-harness-distribution'!$V$7,'agent-harness-distribution'!$X$7,'agent-harness-distribution'!$Z$7,'agent-harness-distribution'!$AB$7)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6FA0-4DA0-93C3-476C5CB99FC7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>steipete</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>steipete</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$8:$AB$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$8,'agent-harness-distribution'!$F$8,'agent-harness-distribution'!$H$8,'agent-harness-distribution'!$J$8,'agent-harness-distribution'!$L$8,'agent-harness-distribution'!$N$8,'agent-harness-distribution'!$P$8,'agent-harness-distribution'!$R$8,'agent-harness-distribution'!$T$8,'agent-harness-distribution'!$V$8,'agent-harness-distribution'!$X$8,'agent-harness-distribution'!$Z$8,'agent-harness-distribution'!$AB$8)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>97.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-304A-45E3-9814-892AE5A416FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>steveyegge</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$9:$AB$9</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$9,'agent-harness-distribution'!$F$9,'agent-harness-distribution'!$H$9,'agent-harness-distribution'!$J$9,'agent-harness-distribution'!$L$9,'agent-harness-distribution'!$N$9,'agent-harness-distribution'!$P$9,'agent-harness-distribution'!$R$9,'agent-harness-distribution'!$T$9,'agent-harness-distribution'!$V$9,'agent-harness-distribution'!$X$9,'agent-harness-distribution'!$Z$9,'agent-harness-distribution'!$AB$9)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C63A-4367-864A-EABE2D854CF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="879696239"/>
+        <c:axId val="879690959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="879696239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879690959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="879690959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="879696239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.0562961372273695E-2"/>
+          <c:y val="0.19492556047074475"/>
+          <c:w val="0.86500140938794512"/>
+          <c:h val="0.4455865948678715"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'agent-harness-distribution'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>teamchong</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$1:$AB$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$1,'agent-harness-distribution'!$F$1,'agent-harness-distribution'!$H$1,'agent-harness-distribution'!$J$1,'agent-harness-distribution'!$L$1,'agent-harness-distribution'!$N$1,'agent-harness-distribution'!$P$1,'agent-harness-distribution'!$R$1,'agent-harness-distribution'!$T$1,'agent-harness-distribution'!$V$1,'agent-harness-distribution'!$X$1,'agent-harness-distribution'!$Z$1,'agent-harness-distribution'!$AB$1)</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>amp_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>claude_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>codex_pct</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>copilot_pct</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cursor_pct</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>gastown_pct</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gemini_pct</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>multi_agent_pct</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>no_signal_pct</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>opencode_pct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>pi_pct</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>qwen_code_pct</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>windsurf_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'agent-harness-distribution'!$B$10:$AB$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('agent-harness-distribution'!$D$10,'agent-harness-distribution'!$F$10,'agent-harness-distribution'!$H$10,'agent-harness-distribution'!$J$10,'agent-harness-distribution'!$L$10,'agent-harness-distribution'!$N$10,'agent-harness-distribution'!$P$10,'agent-harness-distribution'!$R$10,'agent-harness-distribution'!$T$10,'agent-harness-distribution'!$V$10,'agent-harness-distribution'!$X$10,'agent-harness-distribution'!$Z$10,'agent-harness-distribution'!$AB$10)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D360-43E7-8E22-CEEA26DC3423}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1496,6 +4442,286 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -2002,6 +5228,3541 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2582,7 +9343,310 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>168729</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>48985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>405493</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA54FC54-4455-4CCB-B2C0-E677FB4AB877}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>141514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>195037</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>117020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3789D4D-FBA4-4BC8-82E0-B53C2745E231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>522514</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>328386</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>146049</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D47CD27-D5C8-45B9-8B00-7C05203026C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>821872</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>168728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>425451</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>137885</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B37F56DE-4B15-43F1-BB7F-96591DEEA9D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>117930</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>3629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>234043</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>156029</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C84D6388-5AC2-4176-A5D1-75BF8332ADD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>4536</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>348343</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>160564</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A3AE492-DB33-4EE8-9A26-9A202D82349A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>441779</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>130628</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78313FB0-1A6C-4D50-8D91-01947F9BE55C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F3648BA-EB12-4499-BBC7-2F12F24248E1}" name="Table1" displayName="Table1" ref="A1:AB10" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:AB10" xr:uid="{8F3648BA-EB12-4499-BBC7-2F12F24248E1}"/>
+  <tableColumns count="28">
+    <tableColumn id="1" xr3:uid="{EA98B5FC-DC33-48A5-8307-774B475EE246}" name="developer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{8C8992C9-94FA-49D1-BE12-89F5223B46CC}" name="commits_total"/>
+    <tableColumn id="3" xr3:uid="{00FC5F10-DCA5-4255-97A9-63D21EFDBE76}" name="amp_count"/>
+    <tableColumn id="4" xr3:uid="{59C54ED2-62E1-4730-9211-12C32DB8BA6E}" name="amp_pct" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{1F0382D4-D4AE-44B6-BF51-DA2AB694AA84}" name="claude_code_count"/>
+    <tableColumn id="6" xr3:uid="{7368E15C-3F52-4C59-BE78-65FEFC896AF8}" name="claude_code_pct" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{041AD0D4-A81C-441F-89CE-42B518FF4BFA}" name="codex_count"/>
+    <tableColumn id="8" xr3:uid="{0E3336A8-0138-4BFC-9E0B-C2EF23220995}" name="codex_pct" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{F8300DDB-AB41-49A0-9121-C0FD4EBE5D60}" name="copilot_count"/>
+    <tableColumn id="10" xr3:uid="{79507842-D5B4-4C1B-9387-E61029405B0E}" name="copilot_pct" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{5DDD0807-6CB1-471E-8CE1-7600FF16586A}" name="cursor_count"/>
+    <tableColumn id="12" xr3:uid="{0A8214D9-B66D-4AAC-A4C3-7F1E87996FB0}" name="cursor_pct" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{DE041210-9A03-4DA3-9667-D5787EFAFAA1}" name="gastown_count"/>
+    <tableColumn id="14" xr3:uid="{D52FF272-2687-42E8-84D9-F2AF83FB32BC}" name="gastown_pct" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{19467E7D-16CB-4C94-8810-A37794BD9C83}" name="gemini_count"/>
+    <tableColumn id="16" xr3:uid="{601F3672-DFE8-4529-BB7F-62A7B3CE6CB3}" name="gemini_pct" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{F4390A90-7576-4A86-98F5-E921C85D79E7}" name="multi_agent_count"/>
+    <tableColumn id="18" xr3:uid="{2712CF2D-BE46-49B1-A2DF-EFE7E0FC15E2}" name="multi_agent_pct" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{230D7396-62E4-4AEB-B3F1-F7072A605010}" name="no_signal_count"/>
+    <tableColumn id="20" xr3:uid="{702BFEC8-9A72-43DC-9319-D8E5FEB93A05}" name="no_signal_pct" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{2CDFA2EB-D627-4A33-8347-81AD333B7E90}" name="opencode_count"/>
+    <tableColumn id="22" xr3:uid="{C59328C9-271F-488B-8FD9-C30810B6B3C5}" name="opencode_pct" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{E38CF4B0-15DB-4555-8313-33C268E428D2}" name="pi_count"/>
+    <tableColumn id="24" xr3:uid="{8D37F7A8-D273-4B9F-BAC1-C580A1FB5AE8}" name="pi_pct" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{EDE2C98E-88A3-45CF-A9BE-A06DAB9EFDFD}" name="qwen_code_count"/>
+    <tableColumn id="26" xr3:uid="{D655CC36-0479-4FE9-83BB-2E9173FDF5B6}" name="qwen_code_pct" dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{941E7770-715E-4504-B45F-53A8E2817A03}" name="windsurf_count"/>
+    <tableColumn id="28" xr3:uid="{EF353681-8376-4E44-B80B-E73FE53CF4CD}" name="windsurf_pct" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2906,33 +9970,33 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="13.36328125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.26953125" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" customWidth="1"/>
+    <col min="18" max="18" width="16.36328125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.54296875" customWidth="1"/>
+    <col min="20" max="20" width="14.453125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" customWidth="1"/>
+    <col min="22" max="22" width="14.7265625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.08984375" customWidth="1"/>
+    <col min="24" max="24" width="8" style="1" customWidth="1"/>
+    <col min="25" max="25" width="18.08984375" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="28" max="28" width="13.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3799,5 +10863,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/figures/rq2/agent-harness-distribution.xlsx
+++ b/figures/rq2/agent-harness-distribution.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\STG\what-are-they-doing\figures\rq2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9A6DA58F-DB5B-4C37-B6F3-DF26C20A0836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE1ECD0-98C6-42E8-9A75-8D6EFE29EA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24789" yWindow="5743" windowWidth="24892" windowHeight="15634" xr2:uid="{A9BDEA09-76A8-4D12-A73E-92A55D0F5EBD}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="21690" xr2:uid="{A9BDEA09-76A8-4D12-A73E-92A55D0F5EBD}"/>
   </bookViews>
   <sheets>
     <sheet name="agent-harness-distribution" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1852,25 +1865,25 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'agent-harness-distribution'!$B$3:$AB$3</c15:sqref>
+                    <c15:sqref>'agent-harness-distribution'!$B$4:$AB$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('agent-harness-distribution'!$D$3,'agent-harness-distribution'!$F$3,'agent-harness-distribution'!$H$3,'agent-harness-distribution'!$J$3,'agent-harness-distribution'!$L$3,'agent-harness-distribution'!$N$3,'agent-harness-distribution'!$P$3,'agent-harness-distribution'!$R$3,'agent-harness-distribution'!$T$3,'agent-harness-distribution'!$V$3,'agent-harness-distribution'!$X$3,'agent-harness-distribution'!$Z$3,'agent-harness-distribution'!$AB$3)</c:f>
+              <c:f>('agent-harness-distribution'!$D$4,'agent-harness-distribution'!$F$4,'agent-harness-distribution'!$H$4,'agent-harness-distribution'!$J$4,'agent-harness-distribution'!$L$4,'agent-harness-distribution'!$N$4,'agent-harness-distribution'!$P$4,'agent-harness-distribution'!$R$4,'agent-harness-distribution'!$T$4,'agent-harness-distribution'!$V$4,'agent-harness-distribution'!$X$4,'agent-harness-distribution'!$Z$4,'agent-harness-distribution'!$AB$4)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.6</c:v>
+                  <c:v>33.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1879,19 +1892,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6</c:v>
+                  <c:v>1.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>70.599999999999994</c:v>
+                  <c:v>60.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.1000000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -9613,37 +9626,37 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F3648BA-EB12-4499-BBC7-2F12F24248E1}" name="Table1" displayName="Table1" ref="A1:AB10" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F3648BA-EB12-4499-BBC7-2F12F24248E1}" name="Table1" displayName="Table1" ref="A1:AB10" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:AB10" xr:uid="{8F3648BA-EB12-4499-BBC7-2F12F24248E1}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{EA98B5FC-DC33-48A5-8307-774B475EE246}" name="developer" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{EA98B5FC-DC33-48A5-8307-774B475EE246}" name="developer" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{8C8992C9-94FA-49D1-BE12-89F5223B46CC}" name="commits_total"/>
     <tableColumn id="3" xr3:uid="{00FC5F10-DCA5-4255-97A9-63D21EFDBE76}" name="amp_count"/>
-    <tableColumn id="4" xr3:uid="{59C54ED2-62E1-4730-9211-12C32DB8BA6E}" name="amp_pct" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{59C54ED2-62E1-4730-9211-12C32DB8BA6E}" name="amp_pct" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{1F0382D4-D4AE-44B6-BF51-DA2AB694AA84}" name="claude_code_count"/>
-    <tableColumn id="6" xr3:uid="{7368E15C-3F52-4C59-BE78-65FEFC896AF8}" name="claude_code_pct" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{7368E15C-3F52-4C59-BE78-65FEFC896AF8}" name="claude_code_pct" dataDxfId="11"/>
     <tableColumn id="7" xr3:uid="{041AD0D4-A81C-441F-89CE-42B518FF4BFA}" name="codex_count"/>
-    <tableColumn id="8" xr3:uid="{0E3336A8-0138-4BFC-9E0B-C2EF23220995}" name="codex_pct" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{0E3336A8-0138-4BFC-9E0B-C2EF23220995}" name="codex_pct" dataDxfId="10"/>
     <tableColumn id="9" xr3:uid="{F8300DDB-AB41-49A0-9121-C0FD4EBE5D60}" name="copilot_count"/>
-    <tableColumn id="10" xr3:uid="{79507842-D5B4-4C1B-9387-E61029405B0E}" name="copilot_pct" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{79507842-D5B4-4C1B-9387-E61029405B0E}" name="copilot_pct" dataDxfId="9"/>
     <tableColumn id="11" xr3:uid="{5DDD0807-6CB1-471E-8CE1-7600FF16586A}" name="cursor_count"/>
-    <tableColumn id="12" xr3:uid="{0A8214D9-B66D-4AAC-A4C3-7F1E87996FB0}" name="cursor_pct" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{0A8214D9-B66D-4AAC-A4C3-7F1E87996FB0}" name="cursor_pct" dataDxfId="8"/>
     <tableColumn id="13" xr3:uid="{DE041210-9A03-4DA3-9667-D5787EFAFAA1}" name="gastown_count"/>
-    <tableColumn id="14" xr3:uid="{D52FF272-2687-42E8-84D9-F2AF83FB32BC}" name="gastown_pct" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{D52FF272-2687-42E8-84D9-F2AF83FB32BC}" name="gastown_pct" dataDxfId="7"/>
     <tableColumn id="15" xr3:uid="{19467E7D-16CB-4C94-8810-A37794BD9C83}" name="gemini_count"/>
-    <tableColumn id="16" xr3:uid="{601F3672-DFE8-4529-BB7F-62A7B3CE6CB3}" name="gemini_pct" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{601F3672-DFE8-4529-BB7F-62A7B3CE6CB3}" name="gemini_pct" dataDxfId="6"/>
     <tableColumn id="17" xr3:uid="{F4390A90-7576-4A86-98F5-E921C85D79E7}" name="multi_agent_count"/>
-    <tableColumn id="18" xr3:uid="{2712CF2D-BE46-49B1-A2DF-EFE7E0FC15E2}" name="multi_agent_pct" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{2712CF2D-BE46-49B1-A2DF-EFE7E0FC15E2}" name="multi_agent_pct" dataDxfId="5"/>
     <tableColumn id="19" xr3:uid="{230D7396-62E4-4AEB-B3F1-F7072A605010}" name="no_signal_count"/>
-    <tableColumn id="20" xr3:uid="{702BFEC8-9A72-43DC-9319-D8E5FEB93A05}" name="no_signal_pct" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{702BFEC8-9A72-43DC-9319-D8E5FEB93A05}" name="no_signal_pct" dataDxfId="4"/>
     <tableColumn id="21" xr3:uid="{2CDFA2EB-D627-4A33-8347-81AD333B7E90}" name="opencode_count"/>
-    <tableColumn id="22" xr3:uid="{C59328C9-271F-488B-8FD9-C30810B6B3C5}" name="opencode_pct" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{C59328C9-271F-488B-8FD9-C30810B6B3C5}" name="opencode_pct" dataDxfId="3"/>
     <tableColumn id="23" xr3:uid="{E38CF4B0-15DB-4555-8313-33C268E428D2}" name="pi_count"/>
-    <tableColumn id="24" xr3:uid="{8D37F7A8-D273-4B9F-BAC1-C580A1FB5AE8}" name="pi_pct" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{8D37F7A8-D273-4B9F-BAC1-C580A1FB5AE8}" name="pi_pct" dataDxfId="2"/>
     <tableColumn id="25" xr3:uid="{EDE2C98E-88A3-45CF-A9BE-A06DAB9EFDFD}" name="qwen_code_count"/>
-    <tableColumn id="26" xr3:uid="{D655CC36-0479-4FE9-83BB-2E9173FDF5B6}" name="qwen_code_pct" dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{D655CC36-0479-4FE9-83BB-2E9173FDF5B6}" name="qwen_code_pct" dataDxfId="1"/>
     <tableColumn id="27" xr3:uid="{941E7770-715E-4504-B45F-53A8E2817A03}" name="windsurf_count"/>
-    <tableColumn id="28" xr3:uid="{EF353681-8376-4E44-B80B-E73FE53CF4CD}" name="windsurf_pct" dataDxfId="2"/>
+    <tableColumn id="28" xr3:uid="{EF353681-8376-4E44-B80B-E73FE53CF4CD}" name="windsurf_pct" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
